--- a/data/obx_xlsx/MEDI.OL.xlsx
+++ b/data/obx_xlsx/MEDI.OL.xlsx
@@ -12035,10 +12035,18 @@
       </c>
       <c r="N82" s="14"/>
       <c r="O82" s="14"/>
-      <c r="P82" s="14"/>
-      <c r="Q82" s="14"/>
-      <c r="R82" s="14"/>
-      <c r="S82" s="14"/>
+      <c r="P82" s="14">
+        <v>0.0</v>
+      </c>
+      <c r="Q82" s="16">
+        <v>3.0</v>
+      </c>
+      <c r="R82" s="16">
+        <v>4.0</v>
+      </c>
+      <c r="S82" s="16">
+        <v>4.8</v>
+      </c>
       <c r="T82" s="14"/>
       <c r="U82" s="14"/>
       <c r="V82" s="14"/>
